--- a/SLR/Full-Paper-Read/Paper-Review/PS06.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS06.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -26,154 +26,76 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>In the context of smart cities, the paper discusses challenges with big data ecosystem. Interesting topics like crowsensing (where many users collect data) are discussed. They also talk about the 4 V's of big data: volume, variety, velocity and veracity (i.e. how "true" the data is). The auhthors list a couple of projects, papers, solutions or tools that are good to solve some of the problems. It seems that some solutions are research projects, like "4.2 Smart Environment Projects" where a campus with sensors is discussed There is no clear use case, and not data collection or evaluation. Just a discussion of smart cities, some challenges and proposed solutions.</t>
+    <t>The paper motivates the need for elasticity in the process of integrating processes, people, and things. They identify the following aspects important for future integration, reusability, smart things, adatopn, human-based computing. The paper discuss if current practices are capable to capture these concerns. They argue that new emerging concerns need to be adressed in order to acheive elastic systems, but the paper mostly discusses a vision for this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper frames elasticity in the framing of cyber-physical ecosystems, but mostly disucss the term elastic and its place in engineering. </t>
+  </si>
+  <si>
+    <t>CPS Case Study / Example availability</t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>CPS Case Study / Example availability</t>
-  </si>
-  <si>
-    <t>Smart city</t>
-  </si>
-  <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Intelligence and automation</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>People, heterogenity, buisness, re-usability, stakeholder engagement</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ1?</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">These seem to be suggestions or research projects that have proposed ot made solutions. TRL 2-3???
-ParticipAct - mobile crowdsourcing platform -- Cardone, G., Corradi, A., Foschini, L., Ianniello, R.: ParticipAct: a large-scale crowdsensing platform. IEEE Trans. Emerg. Top. Comput. 4(1), 21–32 (2015)
-SmartCampus experiment -- Cecchinel, C., Jimenez, M., Mosser, S., Riveill, M.: An architecture to support the collection of big data in the Internet of Things. In: IEEE World Congress on Services (SERVICES), pp. 442–449 (2014)
-The Available Network Gateways in Edge Location Services (ANGELS) framework appeared as a result of the realization of the complexity of new applications in cyber-physical systems -- Mukherjee, A., Paul, H.S., Dey, S., Banerjee, A.: Angels for distributed analytics in IoT. In: IEEE World Forum on Internet of Things (WF-IoT), pp. 565–570 (2014)
-</t>
-  </si>
-  <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Continuous software and system engineering</t>
-  </si>
-  <si>
-    <t>Intelligence and automation</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>Cybersecurity, heterogeneity , energy/resource consumption, veracity (true data)</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ1?</t>
-  </si>
-  <si>
-    <t>They disucss some problems of smart cities.</t>
+    <t>Yes, since the discussed topic is related to ecosystems. But, the paper is not mainly interested in the topic related to RQ1, but discusses it nontehteless</t>
   </si>
   <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>Yes, but I can't tell if these have TRL1, 2, 3 or more (see tools)</t>
-  </si>
-  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
     <t>Digital Life</t>
   </si>
   <si>
+    <t>Cloud computing, IoT, IT, Human-based computing</t>
+  </si>
+  <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
   </si>
   <si>
-    <t>Challenges</t>
-  </si>
-  <si>
-    <t>Random notes from Per</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - heterogeneity in communicaiton technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - border between social and technical challnges not clear</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - heterogeneity in APIs</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - crowdsensing</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - keeping users (that are part of the ecosystem) engaged</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - "Volume, variety and velocity of the data are driven by the data quality assurance needs..."</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - growing infrastructure to handle big data</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 4'th V: Veracity (How true it is?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - minimize resource overhead (energy)</t>
-  </si>
-  <si>
-    <t>RQ1 In the SECO, what are the main challenges faced during the CPS development?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - identify users that can participate in data collection campaign</t>
-  </si>
-  <si>
-    <t>RQ2 How do industry and academia collaborate and benefit in the SECO for CPS development?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - From IoT to middleware: "heterogeneity, interoperability, security and dependability."</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - "using cloud-based platforms to host sensor networks is one of the biggest challenges yet"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Section 3.2: 
-   - support for spatio-temporal queries
-   - minimal overhead on IoT nodes
-   - Openness and security
-   - fast feedback and minimal delay in producing quality-aware sensing data</t>
-  </si>
-  <si>
-    <t>Solution (section 4)
- - Crowssensing-based IoT-Big Data Projects
- - Smart Environment Projects
- - Edge Computing Based Projects
- - Big data stream analysis projects for cybserphysical systems
- - Distributed, Secure, Scalable Storage of IoT Data
- - Quality of Data (QoD)-Aware IoT Big Data Projects
- - Spatial Big Data Projects</t>
-  </si>
-  <si>
-    <t>Last section</t>
-  </si>
-  <si>
-    <t>"the majority of the data will still be unstructured and untagged.Therefore, collec tion of the data, proper tagging and structuring to improve the value of the IoT data is critical"</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Data overload: Finally, IoT sensors will push IoT data continuously, and typically in raw form to be processed so to produce value. Hence, development of scalable and analytics-backed visualization mechanisms for long term data is also important to prevent data overloads for the IoT-big data systems</t>
+    <t xml:space="preserve">This is an opinion paper, with quite low validity in my opinion, missing many parts of what would be expected for this kind of paper. </t>
+  </si>
+  <si>
+    <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
+  </si>
+  <si>
+    <t>RQ2: How do industry and academia collaborate and benefit in the SECO for CPS development?</t>
   </si>
   <si>
     <t>Assessment Criterion (Question)</t>
@@ -279,7 +201,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -306,15 +228,9 @@
     </font>
     <font/>
     <font>
+      <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Lato"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -649,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -668,7 +584,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -682,16 +598,13 @@
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -703,12 +616,15 @@
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -718,84 +634,81 @@
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1093,7 +1006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="103.5" customHeight="1">
+    <row r="3" ht="82.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1112,7 +1025,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1139,7 +1052,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1147,28 +1060,28 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="G6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="22" t="s">
         <v>15</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1176,37 +1089,37 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="22" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="23" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="B8" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="23" t="s">
-        <v>21</v>
+      <c r="I8" s="27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1214,18 +1127,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+        <v>20</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="28" t="s">
-        <v>5</v>
+      <c r="I9" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1233,28 +1146,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1262,118 +1175,45 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="31">
         <f>Quality!C29</f>
-        <v>3.333333333</v>
-      </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="28" t="s">
-        <v>5</v>
+        <v>4.074074074</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="32" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13">
-      <c r="B13" s="32" t="s">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="B14" s="33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="B15" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="B16" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="B17" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="B18" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="B19" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="B20" s="32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>44</v>
-      </c>
-    </row>
+    </row>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="D25" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="D26" s="32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="D27" s="32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="D28" s="32" t="s">
-        <v>48</v>
-      </c>
-    </row>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2419,10 +2259,10 @@
     <row r="1">
       <c r="A1" s="34"/>
       <c r="B1" s="35" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D1" s="36"/>
       <c r="E1" s="37"/>
@@ -2430,13 +2270,13 @@
     </row>
     <row r="2">
       <c r="A2" s="39" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C2" s="41">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
@@ -2445,9 +2285,9 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="41">
+        <v>32</v>
+      </c>
+      <c r="C3" s="44">
         <v>0.5</v>
       </c>
       <c r="D3" s="36"/>
@@ -2457,10 +2297,10 @@
     <row r="4">
       <c r="A4" s="43"/>
       <c r="B4" s="40" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C4" s="44">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="36"/>
@@ -2468,9 +2308,9 @@
     <row r="5">
       <c r="A5" s="43"/>
       <c r="B5" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="44">
+        <v>34</v>
+      </c>
+      <c r="C5" s="41">
         <v>1.0</v>
       </c>
       <c r="D5" s="36"/>
@@ -2479,9 +2319,9 @@
     <row r="6">
       <c r="A6" s="43"/>
       <c r="B6" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="41">
+        <v>35</v>
+      </c>
+      <c r="C6" s="44">
         <v>0.5</v>
       </c>
       <c r="D6" s="36"/>
@@ -2490,9 +2330,9 @@
     <row r="7">
       <c r="A7" s="45"/>
       <c r="B7" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="44">
+        <v>36</v>
+      </c>
+      <c r="C7" s="41">
         <v>1.0</v>
       </c>
       <c r="D7" s="46">
@@ -2506,13 +2346,13 @@
     </row>
     <row r="8">
       <c r="A8" s="47" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C8" s="49">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
@@ -2520,10 +2360,10 @@
     <row r="9">
       <c r="A9" s="43"/>
       <c r="B9" s="48" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C9" s="49">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
@@ -2531,10 +2371,10 @@
     <row r="10">
       <c r="A10" s="43"/>
       <c r="B10" s="48" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C10" s="49">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
@@ -2542,7 +2382,7 @@
     <row r="11">
       <c r="A11" s="43"/>
       <c r="B11" s="48" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C11" s="49">
         <v>0.0</v>
@@ -2553,7 +2393,7 @@
     <row r="12">
       <c r="A12" s="43"/>
       <c r="B12" s="48" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C12" s="49">
         <v>0.0</v>
@@ -2564,7 +2404,7 @@
     <row r="13">
       <c r="A13" s="43"/>
       <c r="B13" s="48" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C13" s="49">
         <v>0.0</v>
@@ -2575,7 +2415,7 @@
     <row r="14">
       <c r="A14" s="43"/>
       <c r="B14" s="48" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C14" s="49">
         <v>0.5</v>
@@ -2586,7 +2426,7 @@
     <row r="15">
       <c r="A15" s="43"/>
       <c r="B15" s="48" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C15" s="49">
         <v>0.5</v>
@@ -2597,7 +2437,7 @@
     <row r="16">
       <c r="A16" s="43"/>
       <c r="B16" s="48" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C16" s="49">
         <v>0.0</v>
@@ -2608,10 +2448,10 @@
     <row r="17">
       <c r="A17" s="43"/>
       <c r="B17" s="48" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C17" s="49">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -2619,7 +2459,7 @@
     <row r="18">
       <c r="A18" s="43"/>
       <c r="B18" s="48" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C18" s="49">
         <v>0.0</v>
@@ -2630,10 +2470,10 @@
     <row r="19">
       <c r="A19" s="45"/>
       <c r="B19" s="48" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C19" s="49">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D19" s="46">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2641,18 +2481,18 @@
       </c>
       <c r="E19" s="46">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>0.8333333333</v>
+        <v>2.916666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C20" s="52">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
@@ -2660,9 +2500,9 @@
     <row r="21">
       <c r="A21" s="43"/>
       <c r="B21" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="53">
+        <v>52</v>
+      </c>
+      <c r="C21" s="52">
         <v>0.0</v>
       </c>
       <c r="D21" s="36"/>
@@ -2671,9 +2511,9 @@
     <row r="22">
       <c r="A22" s="43"/>
       <c r="B22" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="53">
+        <v>53</v>
+      </c>
+      <c r="C22" s="52">
         <v>0.0</v>
       </c>
       <c r="D22" s="36"/>
@@ -2682,9 +2522,9 @@
     <row r="23">
       <c r="A23" s="43"/>
       <c r="B23" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="53">
+        <v>54</v>
+      </c>
+      <c r="C23" s="52">
         <v>0.0</v>
       </c>
       <c r="D23" s="37"/>
@@ -2694,10 +2534,10 @@
     <row r="24">
       <c r="A24" s="43"/>
       <c r="B24" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="53">
-        <v>0.0</v>
+        <v>55</v>
+      </c>
+      <c r="C24" s="52">
+        <v>0.5</v>
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="37"/>
@@ -2706,30 +2546,30 @@
     <row r="25">
       <c r="A25" s="45"/>
       <c r="B25" s="51" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C25" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="53">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="53">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>3.333333333</v>
+        <v>1.666666667</v>
       </c>
       <c r="F25" s="42"/>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="57">
-        <v>1.0</v>
+      <c r="A26" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="56">
+        <v>0.5</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -2737,11 +2577,11 @@
     </row>
     <row r="27">
       <c r="A27" s="43"/>
-      <c r="B27" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="58">
-        <v>0.5</v>
+      <c r="B27" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="57">
+        <v>1.0</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="37"/>
@@ -2749,30 +2589,30 @@
     </row>
     <row r="28">
       <c r="A28" s="45"/>
-      <c r="B28" s="56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="D28" s="54">
+      <c r="B28" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="D28" s="53">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="53">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>5</v>
+        <v>6.666666667</v>
       </c>
       <c r="F28" s="42"/>
     </row>
     <row r="29">
-      <c r="B29" s="59">
+      <c r="B29" s="58">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="58">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>3.333333333</v>
+        <v>4.074074074</v>
       </c>
     </row>
   </sheetData>
